--- a/MinMax/scripts/comparison/accuracy_comparison_table_57_2_False.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_57_2_False.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="34">
   <si>
     <t>Pg Vm Projection False</t>
   </si>
@@ -31,88 +31,91 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>Ibr_from_r_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
+    <t>qg_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
+    <t>pinj_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>slack_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
     <t>pg_tot</t>
   </si>
   <si>
     <t>Iinj_i_tot</t>
   </si>
   <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>slack_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>pinj_tot</t>
-  </si>
-  <si>
-    <t>Ibr_from_r_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>solve_time</t>
-  </si>
-  <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>28112.80 (23677.68 &gt; 18.78%)</t>
-  </si>
-  <si>
-    <t>1.38 (2.45)</t>
-  </si>
-  <si>
-    <t>0.45s (0.28 s)</t>
-  </si>
-  <si>
-    <t>23871.08 (23677.68 &gt; 0.82%)</t>
+    <t>0.41s (0.29 s)</t>
+  </si>
+  <si>
+    <t>1.49 (2.45)</t>
+  </si>
+  <si>
+    <t>28671.70 (24474.61 &gt; 17.15%)</t>
+  </si>
+  <si>
+    <t>0.12s (0.29 s)</t>
   </si>
   <si>
     <t>2.34 (2.45)</t>
   </si>
   <si>
-    <t>0.14s (0.28 s)</t>
-  </si>
-  <si>
-    <t>23680.20 (23677.68 &gt; 0.01%)</t>
+    <t>24680.93 (24474.61 &gt; 0.84%)</t>
+  </si>
+  <si>
+    <t>0.31s (0.29 s)</t>
   </si>
   <si>
     <t>2.45 (2.45)</t>
   </si>
   <si>
-    <t>0.27s (0.28 s)</t>
-  </si>
-  <si>
-    <t>0.23s (0.28 s)</t>
+    <t>24477.39 (24474.61 &gt; 0.01%)</t>
+  </si>
+  <si>
+    <t>0.22s (0.29 s)</t>
   </si>
 </sst>
 </file>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -495,16 +498,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>1.179198902753544E-17</v>
+        <v>0.008265250362455845</v>
       </c>
       <c r="C2">
-        <v>1.179198902753544E-17</v>
+        <v>6.735224451404065E-05</v>
       </c>
       <c r="D2">
-        <v>1.179198902753544E-17</v>
+        <v>7.162692054407671E-05</v>
       </c>
       <c r="E2">
-        <v>1.179198902753544E-17</v>
+        <v>9.889150533126667E-05</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -512,16 +515,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>8.651482582092285</v>
+        <v>0.3425585925579071</v>
       </c>
       <c r="C3">
-        <v>0.009345434606075287</v>
+        <v>0.002274195197969675</v>
       </c>
       <c r="D3">
-        <v>1.226379851004822E-07</v>
+        <v>0.001926628407090902</v>
       </c>
       <c r="E3">
-        <v>1.226379851004822E-07</v>
+        <v>0.003328903112560511</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -529,33 +532,33 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0.002721100812777877</v>
+        <v>0.00127755431458354</v>
       </c>
       <c r="C4">
-        <v>0.002626470057293773</v>
+        <v>0.0001454377925256267</v>
       </c>
       <c r="D4">
-        <v>0.0009043255704455078</v>
+        <v>0.0001409962715115398</v>
       </c>
       <c r="E4">
-        <v>0.0009043255704455078</v>
+        <v>0.0001505498948972672</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
+      <c r="B5">
+        <v>0.01339857373386621</v>
+      </c>
+      <c r="C5">
+        <v>0.004085067193955183</v>
+      </c>
+      <c r="D5">
+        <v>0.002243997529149055</v>
+      </c>
+      <c r="E5">
+        <v>0.003144488902762532</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -563,33 +566,33 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0.919338583946228</v>
+        <v>0.1243216842412949</v>
       </c>
       <c r="C6">
-        <v>0.001156468177214265</v>
+        <v>0.03545558452606201</v>
       </c>
       <c r="D6">
-        <v>4.557110059977276E-06</v>
+        <v>0.01824688538908958</v>
       </c>
       <c r="E6">
-        <v>4.557110059977276E-06</v>
+        <v>0.02739138714969158</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" t="s">
-        <v>30</v>
+      <c r="B7">
+        <v>0.002752037718892097</v>
+      </c>
+      <c r="C7">
+        <v>0.002757957670837641</v>
+      </c>
+      <c r="D7">
+        <v>0.001221247599460185</v>
+      </c>
+      <c r="E7">
+        <v>0.003067263402044773</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -597,33 +600,33 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.007431769277900457</v>
+        <v>0.003428516676649451</v>
       </c>
       <c r="C8">
-        <v>3.086937067564577E-05</v>
+        <v>0.001149525283835828</v>
       </c>
       <c r="D8">
-        <v>6.562452654179651E-06</v>
+        <v>0.0009576885495334864</v>
       </c>
       <c r="E8">
-        <v>6.562452654179651E-06</v>
+        <v>0.001147493254393339</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9">
-        <v>0.1025990545749664</v>
-      </c>
-      <c r="C9">
-        <v>0.02131626754999161</v>
-      </c>
-      <c r="D9">
-        <v>0.004765178542584181</v>
-      </c>
-      <c r="E9">
-        <v>0.004765178542584181</v>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -631,50 +634,38 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0.002070246729999781</v>
+        <v>0.00339048053137958</v>
       </c>
       <c r="C10">
-        <v>0.0008336665341630578</v>
+        <v>0.001139517175033689</v>
       </c>
       <c r="D10">
-        <v>0.0004964048275724053</v>
+        <v>0.0009474768303334713</v>
       </c>
       <c r="E10">
-        <v>0.0004964048275724053</v>
+        <v>0.001136411796323955</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11">
-        <v>6.066369421523152E-19</v>
-      </c>
-      <c r="C11">
-        <v>6.066369421523152E-19</v>
-      </c>
-      <c r="D11">
-        <v>6.066369421523152E-19</v>
-      </c>
-      <c r="E11">
-        <v>6.066369421523152E-19</v>
-      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.9309866428375244</v>
+        <v>0.0001482923835283145</v>
       </c>
       <c r="C12">
-        <v>0.001181130646727979</v>
+        <v>0.000134875561343506</v>
       </c>
       <c r="D12">
-        <v>1.290111661944593E-08</v>
+        <v>0.000131361186504364</v>
       </c>
       <c r="E12">
-        <v>1.290111661944593E-08</v>
+        <v>0.0001175383149529807</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -682,16 +673,16 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0.3342661261558533</v>
+        <v>0.9402258396148682</v>
       </c>
       <c r="C13">
-        <v>0.0004355317796580493</v>
+        <v>0.005875900387763977</v>
       </c>
       <c r="D13">
-        <v>4.458616331248777E-06</v>
+        <v>0.004925866611301899</v>
       </c>
       <c r="E13">
-        <v>4.458616331248777E-06</v>
+        <v>0.008309087716042995</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -699,50 +690,50 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.001337319263257086</v>
+        <v>0.9305751323699951</v>
       </c>
       <c r="C14">
-        <v>0.0001267422630917281</v>
+        <v>0.005656037945300341</v>
       </c>
       <c r="D14">
-        <v>0.0001116096900659613</v>
+        <v>0.004579057451337576</v>
       </c>
       <c r="E14">
-        <v>0.0001116096900659613</v>
+        <v>0.007991922087967396</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
-        <v>0.002039699116721749</v>
-      </c>
-      <c r="C15">
-        <v>0.0008258976740762591</v>
-      </c>
-      <c r="D15">
-        <v>0.0004885719972662628</v>
-      </c>
-      <c r="E15">
-        <v>0.0004885719972662628</v>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B16">
-        <v>0.3348852396011353</v>
-      </c>
-      <c r="C16">
-        <v>0.0004356935678515583</v>
-      </c>
-      <c r="D16">
-        <v>4.45091791334562E-06</v>
-      </c>
-      <c r="E16">
-        <v>4.45091791334562E-06</v>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -750,33 +741,33 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0.01110085565596819</v>
+        <v>0.3432000875473022</v>
       </c>
       <c r="C17">
-        <v>0.002626738976687193</v>
+        <v>0.002272103447467089</v>
       </c>
       <c r="D17">
-        <v>0.0008567528566345572</v>
+        <v>0.001925089047290385</v>
       </c>
       <c r="E17">
-        <v>0.0008567528566345572</v>
+        <v>0.003328067483380437</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" t="s">
-        <v>32</v>
+      <c r="B18">
+        <v>8.771542549133301</v>
+      </c>
+      <c r="C18">
+        <v>0.06709211319684982</v>
+      </c>
+      <c r="D18">
+        <v>0.05984580889344215</v>
+      </c>
+      <c r="E18">
+        <v>0.09760244935750961</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -784,16 +775,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.001102066482417285</v>
+        <v>0.006002508103847504</v>
       </c>
       <c r="C19">
-        <v>0.0001317410642514005</v>
+        <v>0.003707675030454993</v>
       </c>
       <c r="D19">
-        <v>0.0001138017687480897</v>
+        <v>0.002374582923948765</v>
       </c>
       <c r="E19">
-        <v>0.0001138017687480897</v>
+        <v>0.002966339001432061</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.001022047712467611</v>
+      </c>
+      <c r="C20">
+        <v>0.0001471134892199188</v>
+      </c>
+      <c r="D20">
+        <v>0.0001396629668306559</v>
+      </c>
+      <c r="E20">
+        <v>0.000148288017953746</v>
       </c>
     </row>
   </sheetData>
